--- a/Master/6135r00/6135r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/6135r00/6135r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1434,322 +1434,342 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>5.129</v>
+        <v>1.237</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>6.86</v>
+        <v>6.8323</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>-1.4897</v>
+        <v>-3.7387</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0184</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>2.129</v>
+        <v>5.129</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>6.8636</v>
+        <v>6.86</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-1.624</v>
+        <v>-1.4897</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.0103</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>3.13</v>
+        <v>2.129</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>6.9662</v>
+        <v>6.8636</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>-1.8163</v>
+        <v>-1.624</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.0152</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>6.13</v>
+        <v>3.13</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C53" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>6.9677</v>
+        <v>6.9662</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-1.6974</v>
+        <v>-1.8163</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>4.131</v>
+        <v>6.13</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C54" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>7.0535</v>
+        <v>6.9677</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>-2.0264</v>
+        <v>-1.6974</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0071</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>1.131</v>
+        <v>4.131</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C55" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>7.0538</v>
+        <v>7.0535</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-2.1475</v>
+        <v>-2.0264</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.0124</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>2.132</v>
+        <v>1.131</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>7.1227</v>
+        <v>7.0538</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>-2.3589</v>
+        <v>-2.1475</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>0.006</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>5.132</v>
+        <v>2.132</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C57" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>7.124</v>
+        <v>7.1227</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-2.233</v>
+        <v>-2.3589</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.0095</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>6.133</v>
+        <v>5.132</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>7.1825</v>
+        <v>7.124</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>-2.4326</v>
+        <v>-2.233</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0.0056</v>
+        <v>0.0095</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>3.133</v>
+        <v>6.133</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>7.1837</v>
+        <v>7.1825</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-2.5568</v>
+        <v>-2.4326</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>4.134</v>
+        <v>3.133</v>
       </c>
       <c r="B60" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>7.2366</v>
+        <v>7.1837</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>-2.7614</v>
+        <v>-2.5568</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.0047</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>1.134</v>
+        <v>4.134</v>
       </c>
       <c r="B61" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C61" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>7.2376</v>
+        <v>7.2366</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-2.8857</v>
+        <v>-2.7614</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0047</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>2.135</v>
+        <v>1.134</v>
       </c>
       <c r="B62" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>7.2833</v>
+        <v>7.2376</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>-3.1011</v>
+        <v>-2.8857</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>0.0041</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>5.135</v>
+        <v>2.135</v>
       </c>
       <c r="B63" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C63" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>7.2837</v>
+        <v>7.2833</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-2.9761</v>
+        <v>-3.1011</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>0.0065</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
+        <v>5.135</v>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>7.2837</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>-2.9761</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>0.0065</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
         <v>6.136</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B65" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C64" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="7" t="n">
+      <c r="C65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7" t="n">
         <v>7.322</v>
       </c>
-      <c r="E64" s="7" t="n">
+      <c r="E65" s="7" t="n">
         <v>-3.1919</v>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F65" s="7" t="n">
         <v>0.0033</v>
       </c>
     </row>
-    <row r="66">
-      <c r="E66" s="8" t="inlineStr">
+    <row r="67">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F66" s="9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="E67" s="8" t="inlineStr">
+      <c r="F67" s="9" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F67" s="10" t="n">
-        <v>1.8205</v>
+      <c r="F68" s="10" t="n">
+        <v>1.8207</v>
       </c>
     </row>
   </sheetData>
